--- a/CardData/CardSecondType.xlsx
+++ b/CardData/CardSecondType.xlsx
@@ -226,9 +226,7 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="C15" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="C15" s="3"/>
     </row>
     <row r="16"/>
     <row r="17"/>
